--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="835">
   <si>
     <t>Property</t>
   </si>
@@ -2429,6 +2429,12 @@
   </si>
   <si>
     <t>Attaché de recherche clinique</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
   </si>
   <si>
     <t>365</t>
@@ -5529,7 +5535,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -6138,18 +6144,26 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>42</v>
+        <v>832</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>42</v>
+        <v>833</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>832</v>
+      <c r="B78" t="s" s="2">
+        <v>834</v>
       </c>
     </row>
   </sheetData>
